--- a/data-import/import_producao.xlsx
+++ b/data-import/import_producao.xlsx
@@ -397,22 +397,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E137"/>
+  <dimension ref="A1:F137"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
         <v>ATA"</v>
       </c>
       <c r="B1" t="str">
+        <v>MAQUINA</v>
+      </c>
+      <c r="C1" t="str">
         <v>CODIGO</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>QTD</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>DESCRICAO</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>DESTINO</v>
       </c>
     </row>
@@ -420,16 +423,19 @@
       <c r="A2">
         <v>45972.87467592592</v>
       </c>
-      <c r="B2">
+      <c r="B2" t="str">
+        <v>Conformadora de Telhas</v>
+      </c>
+      <c r="C2">
         <v>2014</v>
       </c>
-      <c r="C2">
+      <c r="D2">
         <v>100</v>
       </c>
-      <c r="D2" t="str">
+      <c r="E2" t="str">
         <v>TELHA GALVALUME OND 17 0,43MM 4,00M</v>
       </c>
-      <c r="E2" t="str">
+      <c r="F2" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -437,16 +443,19 @@
       <c r="A3">
         <v>45972.87467592592</v>
       </c>
-      <c r="B3">
-        <v>2000</v>
+      <c r="B3" t="str">
+        <v>Conformadora de Telhas</v>
       </c>
       <c r="C3">
+        <v>2000</v>
+      </c>
+      <c r="D3">
         <v>51</v>
       </c>
-      <c r="D3" t="str">
-        <v>TELHA GALVALUME TP 40 0,43MM</v>
-      </c>
       <c r="E3" t="str">
+        <v>TELHA GALVALUME TP 40 0,43MM</v>
+      </c>
+      <c r="F3" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -455,15 +464,18 @@
         <v>45972.87467592592</v>
       </c>
       <c r="B4" t="str">
+        <v>Perfil "U" BR200 Regiane</v>
+      </c>
+      <c r="C4" t="str">
         <v>00651k</v>
       </c>
-      <c r="C4">
+      <c r="D4">
         <v>635</v>
       </c>
-      <c r="D4" t="str">
+      <c r="E4" t="str">
         <v>PERFIL US 50X25X1,95 GALV</v>
       </c>
-      <c r="E4" t="str">
+      <c r="F4" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -472,15 +484,18 @@
         <v>45972.87467592592</v>
       </c>
       <c r="B5" t="str">
+        <v>Perfil "U" Marafon</v>
+      </c>
+      <c r="C5" t="str">
         <v>00670k</v>
       </c>
-      <c r="C5">
+      <c r="D5">
         <v>320</v>
       </c>
-      <c r="D5" t="str">
+      <c r="E5" t="str">
         <v>PERFIL UE 75X40X15X1,95 GALV</v>
       </c>
-      <c r="E5" t="str">
+      <c r="F5" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -488,16 +503,19 @@
       <c r="A6">
         <v>45973.87467592592</v>
       </c>
-      <c r="B6">
+      <c r="B6" t="str">
+        <v>Conformadora de Telhas</v>
+      </c>
+      <c r="C6">
         <v>2017</v>
       </c>
-      <c r="C6">
+      <c r="D6">
         <v>100</v>
       </c>
-      <c r="D6" t="str">
+      <c r="E6" t="str">
         <v>TELHA GALVALUME OND 17 0,43MM 7,00M</v>
       </c>
-      <c r="E6" t="str">
+      <c r="F6" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -505,16 +523,19 @@
       <c r="A7">
         <v>45973.87467592592</v>
       </c>
-      <c r="B7">
+      <c r="B7" t="str">
+        <v>Conformadora de Telhas</v>
+      </c>
+      <c r="C7">
         <v>2016</v>
       </c>
-      <c r="C7">
+      <c r="D7">
         <v>200</v>
       </c>
-      <c r="D7" t="str">
+      <c r="E7" t="str">
         <v>TELHA GALVALUME OND 17 0,43MM 6,00M</v>
       </c>
-      <c r="E7" t="str">
+      <c r="F7" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -522,16 +543,19 @@
       <c r="A8">
         <v>45973.87467592592</v>
       </c>
-      <c r="B8">
+      <c r="B8" t="str">
+        <v>Conformadora de Telhas</v>
+      </c>
+      <c r="C8">
         <v>2015</v>
       </c>
-      <c r="C8">
+      <c r="D8">
         <v>100</v>
       </c>
-      <c r="D8" t="str">
+      <c r="E8" t="str">
         <v>TELHA GALVALUME OND 17 0,43MM 5,00M</v>
       </c>
-      <c r="E8" t="str">
+      <c r="F8" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -539,16 +563,19 @@
       <c r="A9">
         <v>45973.87467592592</v>
       </c>
-      <c r="B9">
-        <v>2000</v>
+      <c r="B9" t="str">
+        <v>Conformadora de Telhas</v>
       </c>
       <c r="C9">
+        <v>2000</v>
+      </c>
+      <c r="D9">
         <v>94</v>
       </c>
-      <c r="D9" t="str">
-        <v>TELHA GALVALUME TP 40 0,43MM</v>
-      </c>
       <c r="E9" t="str">
+        <v>TELHA GALVALUME TP 40 0,43MM</v>
+      </c>
+      <c r="F9" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -556,16 +583,19 @@
       <c r="A10">
         <v>45973.87467592592</v>
       </c>
-      <c r="B10">
+      <c r="B10" t="str">
+        <v>Conformadora de Telhas</v>
+      </c>
+      <c r="C10">
         <v>2005</v>
       </c>
-      <c r="C10">
+      <c r="D10">
         <v>100</v>
       </c>
-      <c r="D10" t="str">
+      <c r="E10" t="str">
         <v>TELHA GALVALUME TP 40 0,43MM 5,00M</v>
       </c>
-      <c r="E10" t="str">
+      <c r="F10" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -573,16 +603,19 @@
       <c r="A11">
         <v>45973.87467592592</v>
       </c>
-      <c r="B11">
+      <c r="B11" t="str">
+        <v>Conformadora de Telhas</v>
+      </c>
+      <c r="C11">
         <v>2004</v>
       </c>
-      <c r="C11">
+      <c r="D11">
         <v>100</v>
       </c>
-      <c r="D11" t="str">
+      <c r="E11" t="str">
         <v>TELHA GALVALUME TP 40 0,43MM 4,00M</v>
       </c>
-      <c r="E11" t="str">
+      <c r="F11" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -590,16 +623,19 @@
       <c r="A12">
         <v>45973.87467592592</v>
       </c>
-      <c r="B12">
+      <c r="B12" t="str">
+        <v>Conformadora de Telhas</v>
+      </c>
+      <c r="C12">
         <v>2020</v>
       </c>
-      <c r="C12">
+      <c r="D12">
         <v>218</v>
       </c>
-      <c r="D12" t="str">
+      <c r="E12" t="str">
         <v>TELHA CUMEEIRA GL TRAP 40 ABAS 300MM</v>
       </c>
-      <c r="E12" t="str">
+      <c r="F12" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -608,15 +644,18 @@
         <v>45972.87467592592</v>
       </c>
       <c r="B13" t="str">
+        <v>Perfil "U" BR200 Regiane</v>
+      </c>
+      <c r="C13" t="str">
         <v>00651b</v>
       </c>
-      <c r="C13">
+      <c r="D13">
         <v>749</v>
       </c>
-      <c r="D13" t="str">
+      <c r="E13" t="str">
         <v>PERFIL US 50X25X2,00</v>
       </c>
-      <c r="E13" t="str">
+      <c r="F13" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -625,15 +664,18 @@
         <v>45973.87467592592</v>
       </c>
       <c r="B14" t="str">
+        <v>Perfil "U" BR200 Regiane</v>
+      </c>
+      <c r="C14" t="str">
         <v>00651b</v>
       </c>
-      <c r="C14">
+      <c r="D14">
         <v>635</v>
       </c>
-      <c r="D14" t="str">
+      <c r="E14" t="str">
         <v>PERFIL US 50X25X2,00</v>
       </c>
-      <c r="E14" t="str">
+      <c r="F14" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -641,16 +683,19 @@
       <c r="A15">
         <v>45974.87467592592</v>
       </c>
-      <c r="B15">
+      <c r="B15" t="str">
+        <v>Conformadora de Telhas</v>
+      </c>
+      <c r="C15">
         <v>2020</v>
       </c>
-      <c r="C15">
+      <c r="D15">
         <v>100</v>
       </c>
-      <c r="D15" t="str">
+      <c r="E15" t="str">
         <v>TELHA CUMEEIRA GL TRAP 40 ABAS 300MM</v>
       </c>
-      <c r="E15" t="str">
+      <c r="F15" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -658,16 +703,19 @@
       <c r="A16">
         <v>45974.87467592592</v>
       </c>
-      <c r="B16">
-        <v>2000</v>
+      <c r="B16" t="str">
+        <v>Conformadora de Telhas</v>
       </c>
       <c r="C16">
+        <v>2000</v>
+      </c>
+      <c r="D16">
         <v>155</v>
       </c>
-      <c r="D16" t="str">
-        <v>TELHA GALVALUME TP 40 0,43MM</v>
-      </c>
       <c r="E16" t="str">
+        <v>TELHA GALVALUME TP 40 0,43MM</v>
+      </c>
+      <c r="F16" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -675,16 +723,19 @@
       <c r="A17">
         <v>45970.87467592592</v>
       </c>
-      <c r="B17">
+      <c r="B17" t="str">
+        <v>Conformadora de Telhas</v>
+      </c>
+      <c r="C17">
         <v>2004</v>
       </c>
-      <c r="C17">
+      <c r="D17">
         <v>300</v>
       </c>
-      <c r="D17" t="str">
+      <c r="E17" t="str">
         <v>TELHA GALVALUME TP 40 0,43MM 4,00M</v>
       </c>
-      <c r="E17" t="str">
+      <c r="F17" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -692,16 +743,19 @@
       <c r="A18">
         <v>45970.87467592592</v>
       </c>
-      <c r="B18">
-        <v>2000</v>
+      <c r="B18" t="str">
+        <v>Conformadora de Telhas</v>
       </c>
       <c r="C18">
+        <v>2000</v>
+      </c>
+      <c r="D18">
         <v>10</v>
       </c>
-      <c r="D18" t="str">
-        <v>TELHA GALVALUME TP 40 0,43MM</v>
-      </c>
       <c r="E18" t="str">
+        <v>TELHA GALVALUME TP 40 0,43MM</v>
+      </c>
+      <c r="F18" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -709,16 +763,19 @@
       <c r="A19">
         <v>45970.87467592592</v>
       </c>
-      <c r="B19">
-        <v>2000</v>
+      <c r="B19" t="str">
+        <v>Conformadora de Telhas</v>
       </c>
       <c r="C19">
+        <v>2000</v>
+      </c>
+      <c r="D19">
         <v>11</v>
       </c>
-      <c r="D19" t="str">
-        <v>TELHA GALVALUME TP 40 0,43MM</v>
-      </c>
       <c r="E19" t="str">
+        <v>TELHA GALVALUME TP 40 0,43MM</v>
+      </c>
+      <c r="F19" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -726,16 +783,19 @@
       <c r="A20">
         <v>45970.87467592592</v>
       </c>
-      <c r="B20">
+      <c r="B20" t="str">
+        <v>Conformadora de Telhas</v>
+      </c>
+      <c r="C20">
         <v>2006</v>
       </c>
-      <c r="C20">
+      <c r="D20">
         <v>3</v>
       </c>
-      <c r="D20" t="str">
+      <c r="E20" t="str">
         <v>TELHA GALVALUME TP 40 0,43MM 6,00M</v>
       </c>
-      <c r="E20" t="str">
+      <c r="F20" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -743,16 +803,19 @@
       <c r="A21">
         <v>45970.87467592592</v>
       </c>
-      <c r="B21">
-        <v>2000</v>
+      <c r="B21" t="str">
+        <v>Conformadora de Telhas</v>
       </c>
       <c r="C21">
+        <v>2000</v>
+      </c>
+      <c r="D21">
         <v>3</v>
       </c>
-      <c r="D21" t="str">
-        <v>TELHA GALVALUME TP 40 0,43MM</v>
-      </c>
       <c r="E21" t="str">
+        <v>TELHA GALVALUME TP 40 0,43MM</v>
+      </c>
+      <c r="F21" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -760,16 +823,19 @@
       <c r="A22">
         <v>45970.87467592592</v>
       </c>
-      <c r="B22">
-        <v>2000</v>
+      <c r="B22" t="str">
+        <v>Conformadora de Telhas</v>
       </c>
       <c r="C22">
+        <v>2000</v>
+      </c>
+      <c r="D22">
         <v>3</v>
       </c>
-      <c r="D22" t="str">
-        <v>TELHA GALVALUME TP 40 0,43MM</v>
-      </c>
       <c r="E22" t="str">
+        <v>TELHA GALVALUME TP 40 0,43MM</v>
+      </c>
+      <c r="F22" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -777,16 +843,19 @@
       <c r="A23">
         <v>45970.87467592592</v>
       </c>
-      <c r="B23">
-        <v>2000</v>
+      <c r="B23" t="str">
+        <v>Conformadora de Telhas</v>
       </c>
       <c r="C23">
+        <v>2000</v>
+      </c>
+      <c r="D23">
         <v>3</v>
       </c>
-      <c r="D23" t="str">
-        <v>TELHA GALVALUME TP 40 0,43MM</v>
-      </c>
       <c r="E23" t="str">
+        <v>TELHA GALVALUME TP 40 0,43MM</v>
+      </c>
+      <c r="F23" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -794,16 +863,19 @@
       <c r="A24">
         <v>45970.87467592592</v>
       </c>
-      <c r="B24">
-        <v>2000</v>
+      <c r="B24" t="str">
+        <v>Conformadora de Telhas</v>
       </c>
       <c r="C24">
+        <v>2000</v>
+      </c>
+      <c r="D24">
         <v>3</v>
       </c>
-      <c r="D24" t="str">
-        <v>TELHA GALVALUME TP 40 0,43MM</v>
-      </c>
       <c r="E24" t="str">
+        <v>TELHA GALVALUME TP 40 0,43MM</v>
+      </c>
+      <c r="F24" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -811,16 +883,19 @@
       <c r="A25">
         <v>45970.87467592592</v>
       </c>
-      <c r="B25">
+      <c r="B25" t="str">
+        <v>Conformadora de Telhas</v>
+      </c>
+      <c r="C25">
         <v>2006</v>
       </c>
-      <c r="C25">
+      <c r="D25">
         <v>100</v>
       </c>
-      <c r="D25" t="str">
+      <c r="E25" t="str">
         <v>TELHA GALVALUME TP 40 0,43MM 6,00M</v>
       </c>
-      <c r="E25" t="str">
+      <c r="F25" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -828,16 +903,19 @@
       <c r="A26">
         <v>45970.87467592592</v>
       </c>
-      <c r="B26">
+      <c r="B26" t="str">
+        <v>Conformadora de Telhas</v>
+      </c>
+      <c r="C26">
         <v>2005</v>
       </c>
-      <c r="C26">
+      <c r="D26">
         <v>100</v>
       </c>
-      <c r="D26" t="str">
+      <c r="E26" t="str">
         <v>TELHA GALVALUME TP 40 0,43MM 5,00M</v>
       </c>
-      <c r="E26" t="str">
+      <c r="F26" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -845,16 +923,19 @@
       <c r="A27">
         <v>45970.87467592592</v>
       </c>
-      <c r="B27">
+      <c r="B27" t="str">
+        <v>Conformadora de Telhas</v>
+      </c>
+      <c r="C27">
         <v>2003</v>
       </c>
-      <c r="C27">
+      <c r="D27">
         <v>100</v>
       </c>
-      <c r="D27" t="str">
+      <c r="E27" t="str">
         <v>TELHA GALVALUME TP 40 0,43MM 3,00M</v>
       </c>
-      <c r="E27" t="str">
+      <c r="F27" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -862,16 +943,19 @@
       <c r="A28">
         <v>45967.87467592592</v>
       </c>
-      <c r="B28">
-        <v>2000</v>
+      <c r="B28" t="str">
+        <v>Conformadora de Telhas</v>
       </c>
       <c r="C28">
+        <v>2000</v>
+      </c>
+      <c r="D28">
         <v>3</v>
       </c>
-      <c r="D28" t="str">
-        <v>TELHA GALVALUME TP 40 0,43MM</v>
-      </c>
       <c r="E28" t="str">
+        <v>TELHA GALVALUME TP 40 0,43MM</v>
+      </c>
+      <c r="F28" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -879,16 +963,19 @@
       <c r="A29">
         <v>45971.87467592592</v>
       </c>
-      <c r="B29">
+      <c r="B29" t="str">
+        <v>Conformadora de Telhas</v>
+      </c>
+      <c r="C29">
         <v>2006</v>
       </c>
-      <c r="C29">
+      <c r="D29">
         <v>180</v>
       </c>
-      <c r="D29" t="str">
+      <c r="E29" t="str">
         <v>TELHA GALVALUME TP 40 0,43MM 6,00M</v>
       </c>
-      <c r="E29" t="str">
+      <c r="F29" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -896,16 +983,19 @@
       <c r="A30">
         <v>45971.87467592592</v>
       </c>
-      <c r="B30">
+      <c r="B30" t="str">
+        <v>Conformadora de Telhas</v>
+      </c>
+      <c r="C30">
         <v>2005</v>
       </c>
-      <c r="C30">
+      <c r="D30">
         <v>60</v>
       </c>
-      <c r="D30" t="str">
+      <c r="E30" t="str">
         <v>TELHA GALVALUME TP 40 0,43MM 5,00M</v>
       </c>
-      <c r="E30" t="str">
+      <c r="F30" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -913,16 +1003,19 @@
       <c r="A31">
         <v>45971.87467592592</v>
       </c>
-      <c r="B31">
+      <c r="B31" t="str">
+        <v>Conformadora de Telhas</v>
+      </c>
+      <c r="C31">
         <v>2020</v>
       </c>
-      <c r="C31">
+      <c r="D31">
         <v>67</v>
       </c>
-      <c r="D31" t="str">
+      <c r="E31" t="str">
         <v>TELHA CUMEEIRA GL TRAP 40 ABAS 300MM</v>
       </c>
-      <c r="E31" t="str">
+      <c r="F31" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -930,16 +1023,19 @@
       <c r="A32">
         <v>45971.87467592592</v>
       </c>
-      <c r="B32">
+      <c r="B32" t="str">
+        <v>Conformadora de Telhas</v>
+      </c>
+      <c r="C32">
         <v>2006</v>
       </c>
-      <c r="C32">
+      <c r="D32">
         <v>200</v>
       </c>
-      <c r="D32" t="str">
+      <c r="E32" t="str">
         <v>TELHA GALVALUME TP 40 0,43MM 6,00M</v>
       </c>
-      <c r="E32" t="str">
+      <c r="F32" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -947,16 +1043,19 @@
       <c r="A33">
         <v>45963.87467592592</v>
       </c>
-      <c r="B33">
+      <c r="B33" t="str">
+        <v>Conformadora de Telhas</v>
+      </c>
+      <c r="C33">
         <v>2017</v>
       </c>
-      <c r="C33">
+      <c r="D33">
         <v>55</v>
       </c>
-      <c r="D33" t="str">
+      <c r="E33" t="str">
         <v>TELHA GALVALUME OND 17 0,43MM 7,00M</v>
       </c>
-      <c r="E33" t="str">
+      <c r="F33" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -964,16 +1063,19 @@
       <c r="A34">
         <v>45963.87467592592</v>
       </c>
-      <c r="B34">
+      <c r="B34" t="str">
+        <v>Conformadora de Telhas</v>
+      </c>
+      <c r="C34">
         <v>2017</v>
       </c>
-      <c r="C34">
+      <c r="D34">
         <v>45</v>
       </c>
-      <c r="D34" t="str">
+      <c r="E34" t="str">
         <v>TELHA GALVALUME OND 17 0,43MM 7,00M</v>
       </c>
-      <c r="E34" t="str">
+      <c r="F34" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -981,16 +1083,19 @@
       <c r="A35">
         <v>45963.87467592592</v>
       </c>
-      <c r="B35">
+      <c r="B35" t="str">
+        <v>Conformadora de Telhas</v>
+      </c>
+      <c r="C35">
         <v>2004</v>
       </c>
-      <c r="C35">
+      <c r="D35">
         <v>200</v>
       </c>
-      <c r="D35" t="str">
+      <c r="E35" t="str">
         <v>TELHA GALVALUME TP 40 0,43MM 4,00M</v>
       </c>
-      <c r="E35" t="str">
+      <c r="F35" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -998,16 +1103,19 @@
       <c r="A36">
         <v>45963.87467592592</v>
       </c>
-      <c r="B36">
+      <c r="B36" t="str">
+        <v>Conformadora de Telhas</v>
+      </c>
+      <c r="C36">
         <v>2005</v>
       </c>
-      <c r="C36">
+      <c r="D36">
         <v>200</v>
       </c>
-      <c r="D36" t="str">
+      <c r="E36" t="str">
         <v>TELHA GALVALUME TP 40 0,43MM 5,00M</v>
       </c>
-      <c r="E36" t="str">
+      <c r="F36" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -1015,16 +1123,19 @@
       <c r="A37">
         <v>45963.87467592592</v>
       </c>
-      <c r="B37">
+      <c r="B37" t="str">
+        <v>Conformadora de Telhas</v>
+      </c>
+      <c r="C37">
         <v>2006</v>
       </c>
-      <c r="C37">
+      <c r="D37">
         <v>200</v>
       </c>
-      <c r="D37" t="str">
+      <c r="E37" t="str">
         <v>TELHA GALVALUME TP 40 0,43MM 6,00M</v>
       </c>
-      <c r="E37" t="str">
+      <c r="F37" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -1032,16 +1143,19 @@
       <c r="A38">
         <v>45963.87467592592</v>
       </c>
-      <c r="B38">
-        <v>2000</v>
+      <c r="B38" t="str">
+        <v>Conformadora de Telhas</v>
       </c>
       <c r="C38">
+        <v>2000</v>
+      </c>
+      <c r="D38">
         <v>10</v>
       </c>
-      <c r="D38" t="str">
-        <v>TELHA GALVALUME TP 40 0,43MM</v>
-      </c>
       <c r="E38" t="str">
+        <v>TELHA GALVALUME TP 40 0,43MM</v>
+      </c>
+      <c r="F38" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -1049,16 +1163,19 @@
       <c r="A39">
         <v>45963.87467592592</v>
       </c>
-      <c r="B39">
-        <v>2000</v>
+      <c r="B39" t="str">
+        <v>Conformadora de Telhas</v>
       </c>
       <c r="C39">
+        <v>2000</v>
+      </c>
+      <c r="D39">
         <v>10</v>
       </c>
-      <c r="D39" t="str">
-        <v>TELHA GALVALUME TP 40 0,43MM</v>
-      </c>
       <c r="E39" t="str">
+        <v>TELHA GALVALUME TP 40 0,43MM</v>
+      </c>
+      <c r="F39" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -1066,16 +1183,19 @@
       <c r="A40">
         <v>45963.87467592592</v>
       </c>
-      <c r="B40">
-        <v>2000</v>
+      <c r="B40" t="str">
+        <v>Conformadora de Telhas</v>
       </c>
       <c r="C40">
+        <v>2000</v>
+      </c>
+      <c r="D40">
         <v>3</v>
       </c>
-      <c r="D40" t="str">
-        <v>TELHA GALVALUME TP 40 0,43MM</v>
-      </c>
       <c r="E40" t="str">
+        <v>TELHA GALVALUME TP 40 0,43MM</v>
+      </c>
+      <c r="F40" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -1083,16 +1203,19 @@
       <c r="A41">
         <v>45963.87467592592</v>
       </c>
-      <c r="B41">
-        <v>2000</v>
+      <c r="B41" t="str">
+        <v>Conformadora de Telhas</v>
       </c>
       <c r="C41">
+        <v>2000</v>
+      </c>
+      <c r="D41">
         <v>2</v>
       </c>
-      <c r="D41" t="str">
-        <v>TELHA GALVALUME TP 40 0,43MM</v>
-      </c>
       <c r="E41" t="str">
+        <v>TELHA GALVALUME TP 40 0,43MM</v>
+      </c>
+      <c r="F41" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -1100,16 +1223,19 @@
       <c r="A42">
         <v>45963.87467592592</v>
       </c>
-      <c r="B42">
-        <v>2000</v>
+      <c r="B42" t="str">
+        <v>Conformadora de Telhas</v>
       </c>
       <c r="C42">
+        <v>2000</v>
+      </c>
+      <c r="D42">
         <v>10</v>
       </c>
-      <c r="D42" t="str">
-        <v>TELHA GALVALUME TP 40 0,43MM</v>
-      </c>
       <c r="E42" t="str">
+        <v>TELHA GALVALUME TP 40 0,43MM</v>
+      </c>
+      <c r="F42" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -1117,16 +1243,19 @@
       <c r="A43">
         <v>45963.87467592592</v>
       </c>
-      <c r="B43">
-        <v>2000</v>
+      <c r="B43" t="str">
+        <v>Conformadora de Telhas</v>
       </c>
       <c r="C43">
+        <v>2000</v>
+      </c>
+      <c r="D43">
         <v>6</v>
       </c>
-      <c r="D43" t="str">
-        <v>TELHA GALVALUME TP 40 0,43MM</v>
-      </c>
       <c r="E43" t="str">
+        <v>TELHA GALVALUME TP 40 0,43MM</v>
+      </c>
+      <c r="F43" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -1134,16 +1263,19 @@
       <c r="A44">
         <v>45964.87467592592</v>
       </c>
-      <c r="B44">
-        <v>2000</v>
+      <c r="B44" t="str">
+        <v>Conformadora de Telhas</v>
       </c>
       <c r="C44">
+        <v>2000</v>
+      </c>
+      <c r="D44">
         <v>11</v>
       </c>
-      <c r="D44" t="str">
-        <v>TELHA GALVALUME TP 40 0,43MM</v>
-      </c>
       <c r="E44" t="str">
+        <v>TELHA GALVALUME TP 40 0,43MM</v>
+      </c>
+      <c r="F44" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -1151,16 +1283,19 @@
       <c r="A45">
         <v>45964.87467592592</v>
       </c>
-      <c r="B45">
-        <v>2000</v>
+      <c r="B45" t="str">
+        <v>Conformadora de Telhas</v>
       </c>
       <c r="C45">
+        <v>2000</v>
+      </c>
+      <c r="D45">
         <v>21</v>
       </c>
-      <c r="D45" t="str">
-        <v>TELHA GALVALUME TP 40 0,43MM</v>
-      </c>
       <c r="E45" t="str">
+        <v>TELHA GALVALUME TP 40 0,43MM</v>
+      </c>
+      <c r="F45" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -1168,16 +1303,19 @@
       <c r="A46">
         <v>45964.87467592592</v>
       </c>
-      <c r="B46">
+      <c r="B46" t="str">
+        <v>Conformadora de Telhas</v>
+      </c>
+      <c r="C46">
         <v>2007</v>
       </c>
-      <c r="C46">
+      <c r="D46">
         <v>200</v>
       </c>
-      <c r="D46" t="str">
+      <c r="E46" t="str">
         <v>TELHA GALVALUME TP 40 0,43MM 7,00M</v>
       </c>
-      <c r="E46" t="str">
+      <c r="F46" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -1185,16 +1323,19 @@
       <c r="A47">
         <v>45964.87467592592</v>
       </c>
-      <c r="B47">
+      <c r="B47" t="str">
+        <v>Conformadora de Telhas</v>
+      </c>
+      <c r="C47">
         <v>2008</v>
       </c>
-      <c r="C47">
+      <c r="D47">
         <v>62</v>
       </c>
-      <c r="D47" t="str">
+      <c r="E47" t="str">
         <v>TELHA GALVALUME TP 40 0,43MM 8,00M</v>
       </c>
-      <c r="E47" t="str">
+      <c r="F47" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -1202,16 +1343,19 @@
       <c r="A48">
         <v>45964.87467592592</v>
       </c>
-      <c r="B48">
+      <c r="B48" t="str">
+        <v>Conformadora de Telhas</v>
+      </c>
+      <c r="C48">
         <v>2008</v>
       </c>
-      <c r="C48">
+      <c r="D48">
         <v>38</v>
       </c>
-      <c r="D48" t="str">
+      <c r="E48" t="str">
         <v>TELHA GALVALUME TP 40 0,43MM 8,00M</v>
       </c>
-      <c r="E48" t="str">
+      <c r="F48" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -1219,16 +1363,19 @@
       <c r="A49">
         <v>45964.87467592592</v>
       </c>
-      <c r="B49">
+      <c r="B49" t="str">
+        <v>Conformadora de Telhas</v>
+      </c>
+      <c r="C49">
         <v>2017</v>
       </c>
-      <c r="C49">
+      <c r="D49">
         <v>100</v>
       </c>
-      <c r="D49" t="str">
+      <c r="E49" t="str">
         <v>TELHA GALVALUME OND 17 0,43MM 7,00M</v>
       </c>
-      <c r="E49" t="str">
+      <c r="F49" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -1236,16 +1383,19 @@
       <c r="A50">
         <v>45964.87467592592</v>
       </c>
-      <c r="B50">
+      <c r="B50" t="str">
+        <v>Conformadora de Telhas</v>
+      </c>
+      <c r="C50">
         <v>2014</v>
       </c>
-      <c r="C50">
+      <c r="D50">
         <v>200</v>
       </c>
-      <c r="D50" t="str">
+      <c r="E50" t="str">
         <v>TELHA GALVALUME OND 17 0,43MM 4,00M</v>
       </c>
-      <c r="E50" t="str">
+      <c r="F50" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -1253,16 +1403,19 @@
       <c r="A51">
         <v>45965.87467592592</v>
       </c>
-      <c r="B51">
-        <v>2000</v>
+      <c r="B51" t="str">
+        <v>Conformadora de Telhas</v>
       </c>
       <c r="C51">
+        <v>2000</v>
+      </c>
+      <c r="D51">
         <v>26</v>
       </c>
-      <c r="D51" t="str">
-        <v>TELHA GALVALUME TP 40 0,43MM</v>
-      </c>
       <c r="E51" t="str">
+        <v>TELHA GALVALUME TP 40 0,43MM</v>
+      </c>
+      <c r="F51" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -1270,16 +1423,19 @@
       <c r="A52">
         <v>45965.87467592592</v>
       </c>
-      <c r="B52">
-        <v>2000</v>
+      <c r="B52" t="str">
+        <v>Conformadora de Telhas</v>
       </c>
       <c r="C52">
+        <v>2000</v>
+      </c>
+      <c r="D52">
         <v>26</v>
       </c>
-      <c r="D52" t="str">
-        <v>TELHA GALVALUME TP 40 0,43MM</v>
-      </c>
       <c r="E52" t="str">
+        <v>TELHA GALVALUME TP 40 0,43MM</v>
+      </c>
+      <c r="F52" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -1287,16 +1443,19 @@
       <c r="A53">
         <v>45965.87467592592</v>
       </c>
-      <c r="B53">
-        <v>2000</v>
+      <c r="B53" t="str">
+        <v>Conformadora de Telhas</v>
       </c>
       <c r="C53">
+        <v>2000</v>
+      </c>
+      <c r="D53">
         <v>13</v>
       </c>
-      <c r="D53" t="str">
-        <v>TELHA GALVALUME TP 40 0,43MM</v>
-      </c>
       <c r="E53" t="str">
+        <v>TELHA GALVALUME TP 40 0,43MM</v>
+      </c>
+      <c r="F53" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -1304,16 +1463,19 @@
       <c r="A54">
         <v>45965.87467592592</v>
       </c>
-      <c r="B54">
-        <v>2000</v>
+      <c r="B54" t="str">
+        <v>Conformadora de Telhas</v>
       </c>
       <c r="C54">
+        <v>2000</v>
+      </c>
+      <c r="D54">
         <v>26</v>
       </c>
-      <c r="D54" t="str">
-        <v>TELHA GALVALUME TP 40 0,43MM</v>
-      </c>
       <c r="E54" t="str">
+        <v>TELHA GALVALUME TP 40 0,43MM</v>
+      </c>
+      <c r="F54" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -1321,16 +1483,19 @@
       <c r="A55">
         <v>45965.87467592592</v>
       </c>
-      <c r="B55">
-        <v>2000</v>
+      <c r="B55" t="str">
+        <v>Conformadora de Telhas</v>
       </c>
       <c r="C55">
+        <v>2000</v>
+      </c>
+      <c r="D55">
         <v>13</v>
       </c>
-      <c r="D55" t="str">
-        <v>TELHA GALVALUME TP 40 0,43MM</v>
-      </c>
       <c r="E55" t="str">
+        <v>TELHA GALVALUME TP 40 0,43MM</v>
+      </c>
+      <c r="F55" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -1338,16 +1503,19 @@
       <c r="A56">
         <v>45965.87467592592</v>
       </c>
-      <c r="B56">
-        <v>2000</v>
+      <c r="B56" t="str">
+        <v>Conformadora de Telhas</v>
       </c>
       <c r="C56">
+        <v>2000</v>
+      </c>
+      <c r="D56">
         <v>10</v>
       </c>
-      <c r="D56" t="str">
-        <v>TELHA GALVALUME TP 40 0,43MM</v>
-      </c>
       <c r="E56" t="str">
+        <v>TELHA GALVALUME TP 40 0,43MM</v>
+      </c>
+      <c r="F56" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -1355,16 +1523,19 @@
       <c r="A57">
         <v>45965.87467592592</v>
       </c>
-      <c r="B57">
+      <c r="B57" t="str">
+        <v>Conformadora de Telhas</v>
+      </c>
+      <c r="C57">
         <v>2007</v>
       </c>
-      <c r="C57">
+      <c r="D57">
         <v>6</v>
       </c>
-      <c r="D57" t="str">
+      <c r="E57" t="str">
         <v>TELHA GALVALUME TP 40 0,43MM 7,00M</v>
       </c>
-      <c r="E57" t="str">
+      <c r="F57" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -1372,16 +1543,19 @@
       <c r="A58">
         <v>45965.87467592592</v>
       </c>
-      <c r="B58">
+      <c r="B58" t="str">
+        <v>Conformadora de Telhas</v>
+      </c>
+      <c r="C58">
         <v>2005</v>
       </c>
-      <c r="C58">
+      <c r="D58">
         <v>10</v>
       </c>
-      <c r="D58" t="str">
+      <c r="E58" t="str">
         <v>TELHA GALVALUME TP 40 0,43MM 5,00M</v>
       </c>
-      <c r="E58" t="str">
+      <c r="F58" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -1389,16 +1563,19 @@
       <c r="A59">
         <v>45965.87467592592</v>
       </c>
-      <c r="B59">
-        <v>2000</v>
+      <c r="B59" t="str">
+        <v>Conformadora de Telhas</v>
       </c>
       <c r="C59">
+        <v>2000</v>
+      </c>
+      <c r="D59">
         <v>10</v>
       </c>
-      <c r="D59" t="str">
-        <v>TELHA GALVALUME TP 40 0,43MM</v>
-      </c>
       <c r="E59" t="str">
+        <v>TELHA GALVALUME TP 40 0,43MM</v>
+      </c>
+      <c r="F59" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -1406,16 +1583,19 @@
       <c r="A60">
         <v>45965.87467592592</v>
       </c>
-      <c r="B60">
-        <v>2000</v>
+      <c r="B60" t="str">
+        <v>Conformadora de Telhas</v>
       </c>
       <c r="C60">
+        <v>2000</v>
+      </c>
+      <c r="D60">
         <v>4</v>
       </c>
-      <c r="D60" t="str">
-        <v>TELHA GALVALUME TP 40 0,43MM</v>
-      </c>
       <c r="E60" t="str">
+        <v>TELHA GALVALUME TP 40 0,43MM</v>
+      </c>
+      <c r="F60" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -1423,16 +1603,19 @@
       <c r="A61">
         <v>45965.87467592592</v>
       </c>
-      <c r="B61">
-        <v>2000</v>
+      <c r="B61" t="str">
+        <v>Conformadora de Telhas</v>
       </c>
       <c r="C61">
+        <v>2000</v>
+      </c>
+      <c r="D61">
         <v>13</v>
       </c>
-      <c r="D61" t="str">
-        <v>TELHA GALVALUME TP 40 0,43MM</v>
-      </c>
       <c r="E61" t="str">
+        <v>TELHA GALVALUME TP 40 0,43MM</v>
+      </c>
+      <c r="F61" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -1440,16 +1623,19 @@
       <c r="A62">
         <v>45965.87467592592</v>
       </c>
-      <c r="B62">
-        <v>2000</v>
+      <c r="B62" t="str">
+        <v>Conformadora de Telhas</v>
       </c>
       <c r="C62">
+        <v>2000</v>
+      </c>
+      <c r="D62">
         <v>14</v>
       </c>
-      <c r="D62" t="str">
-        <v>TELHA GALVALUME TP 40 0,43MM</v>
-      </c>
       <c r="E62" t="str">
+        <v>TELHA GALVALUME TP 40 0,43MM</v>
+      </c>
+      <c r="F62" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -1457,16 +1643,19 @@
       <c r="A63">
         <v>45971.87467592592</v>
       </c>
-      <c r="B63">
+      <c r="B63" t="str">
+        <v>Conformadora de Telhas</v>
+      </c>
+      <c r="C63">
         <v>2005</v>
       </c>
-      <c r="C63">
+      <c r="D63">
         <v>200</v>
       </c>
-      <c r="D63" t="str">
+      <c r="E63" t="str">
         <v>TELHA GALVALUME TP 40 0,43MM 5,00M</v>
       </c>
-      <c r="E63" t="str">
+      <c r="F63" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -1474,16 +1663,19 @@
       <c r="A64">
         <v>45971.87467592592</v>
       </c>
-      <c r="B64">
+      <c r="B64" t="str">
+        <v>Conformadora de Telhas</v>
+      </c>
+      <c r="C64">
         <v>2003</v>
       </c>
-      <c r="C64">
+      <c r="D64">
         <v>100</v>
       </c>
-      <c r="D64" t="str">
+      <c r="E64" t="str">
         <v>TELHA GALVALUME TP 40 0,43MM 3,00M</v>
       </c>
-      <c r="E64" t="str">
+      <c r="F64" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -1491,16 +1683,19 @@
       <c r="A65">
         <v>45971.87467592592</v>
       </c>
-      <c r="B65">
-        <v>2000</v>
+      <c r="B65" t="str">
+        <v>Conformadora de Telhas</v>
       </c>
       <c r="C65">
+        <v>2000</v>
+      </c>
+      <c r="D65">
         <v>109</v>
       </c>
-      <c r="D65" t="str">
-        <v>TELHA GALVALUME TP 40 0,43MM</v>
-      </c>
       <c r="E65" t="str">
+        <v>TELHA GALVALUME TP 40 0,43MM</v>
+      </c>
+      <c r="F65" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -1508,16 +1703,19 @@
       <c r="A66">
         <v>45965.87467592592</v>
       </c>
-      <c r="B66">
-        <v>2000</v>
+      <c r="B66" t="str">
+        <v>Conformadora de Telhas</v>
       </c>
       <c r="C66">
+        <v>2000</v>
+      </c>
+      <c r="D66">
         <v>24</v>
       </c>
-      <c r="D66" t="str">
-        <v>TELHA GALVALUME TP 40 0,43MM</v>
-      </c>
       <c r="E66" t="str">
+        <v>TELHA GALVALUME TP 40 0,43MM</v>
+      </c>
+      <c r="F66" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -1525,16 +1723,19 @@
       <c r="A67">
         <v>45965.87467592592</v>
       </c>
-      <c r="B67">
-        <v>2000</v>
+      <c r="B67" t="str">
+        <v>Conformadora de Telhas</v>
       </c>
       <c r="C67">
+        <v>2000</v>
+      </c>
+      <c r="D67">
         <v>24</v>
       </c>
-      <c r="D67" t="str">
-        <v>TELHA GALVALUME TP 40 0,43MM</v>
-      </c>
       <c r="E67" t="str">
+        <v>TELHA GALVALUME TP 40 0,43MM</v>
+      </c>
+      <c r="F67" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -1542,16 +1743,19 @@
       <c r="A68">
         <v>45965.87467592592</v>
       </c>
-      <c r="B68">
+      <c r="B68" t="str">
+        <v>Conformadora de Telhas</v>
+      </c>
+      <c r="C68">
         <v>2004</v>
       </c>
-      <c r="C68">
+      <c r="D68">
         <v>18</v>
       </c>
-      <c r="D68" t="str">
+      <c r="E68" t="str">
         <v>TELHA GALVALUME TP 40 0,43MM 4,00M</v>
       </c>
-      <c r="E68" t="str">
+      <c r="F68" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -1559,16 +1763,19 @@
       <c r="A69">
         <v>45965.87467592592</v>
       </c>
-      <c r="B69">
+      <c r="B69" t="str">
+        <v>Conformadora de Telhas</v>
+      </c>
+      <c r="C69">
         <v>2016</v>
       </c>
-      <c r="C69">
+      <c r="D69">
         <v>11</v>
       </c>
-      <c r="D69" t="str">
+      <c r="E69" t="str">
         <v>TELHA GALVALUME OND 17 0,43MM 6,00M</v>
       </c>
-      <c r="E69" t="str">
+      <c r="F69" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -1576,16 +1783,19 @@
       <c r="A70">
         <v>45965.87467592592</v>
       </c>
-      <c r="B70">
+      <c r="B70" t="str">
+        <v>Conformadora de Telhas</v>
+      </c>
+      <c r="C70">
         <v>2016</v>
       </c>
-      <c r="C70">
+      <c r="D70">
         <v>89</v>
       </c>
-      <c r="D70" t="str">
+      <c r="E70" t="str">
         <v>TELHA GALVALUME OND 17 0,43MM 6,00M</v>
       </c>
-      <c r="E70" t="str">
+      <c r="F70" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -1593,16 +1803,19 @@
       <c r="A71">
         <v>45965.87467592592</v>
       </c>
-      <c r="B71">
+      <c r="B71" t="str">
+        <v>Conformadora de Telhas</v>
+      </c>
+      <c r="C71">
         <v>2016</v>
       </c>
-      <c r="C71">
+      <c r="D71">
         <v>100</v>
       </c>
-      <c r="D71" t="str">
+      <c r="E71" t="str">
         <v>TELHA GALVALUME OND 17 0,43MM 6,00M</v>
       </c>
-      <c r="E71" t="str">
+      <c r="F71" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -1610,16 +1823,19 @@
       <c r="A72">
         <v>45966.87467592592</v>
       </c>
-      <c r="B72">
+      <c r="B72" t="str">
+        <v>Conformadora de Telhas</v>
+      </c>
+      <c r="C72">
         <v>2018</v>
       </c>
-      <c r="C72">
+      <c r="D72">
         <v>100</v>
       </c>
-      <c r="D72" t="str">
+      <c r="E72" t="str">
         <v>TELHA GALVALUME OND 17 0,43MM 8,00M</v>
       </c>
-      <c r="E72" t="str">
+      <c r="F72" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -1627,16 +1843,19 @@
       <c r="A73">
         <v>45966.87467592592</v>
       </c>
-      <c r="B73">
+      <c r="B73" t="str">
+        <v>Conformadora de Telhas</v>
+      </c>
+      <c r="C73">
         <v>2017</v>
       </c>
-      <c r="C73">
+      <c r="D73">
         <v>1</v>
       </c>
-      <c r="D73" t="str">
+      <c r="E73" t="str">
         <v>TELHA GALVALUME OND 17 0,43MM 7,00M</v>
       </c>
-      <c r="E73" t="str">
+      <c r="F73" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -1644,16 +1863,19 @@
       <c r="A74">
         <v>45966.87467592592</v>
       </c>
-      <c r="B74">
+      <c r="B74" t="str">
+        <v>Conformadora de Telhas</v>
+      </c>
+      <c r="C74">
         <v>2016</v>
       </c>
-      <c r="C74">
+      <c r="D74">
         <v>100</v>
       </c>
-      <c r="D74" t="str">
+      <c r="E74" t="str">
         <v>TELHA GALVALUME OND 17 0,43MM 6,00M</v>
       </c>
-      <c r="E74" t="str">
+      <c r="F74" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -1661,16 +1883,19 @@
       <c r="A75">
         <v>45966.87467592592</v>
       </c>
-      <c r="B75">
+      <c r="B75" t="str">
+        <v>Conformadora de Telhas</v>
+      </c>
+      <c r="C75">
         <v>2015</v>
       </c>
-      <c r="C75">
+      <c r="D75">
         <v>100</v>
       </c>
-      <c r="D75" t="str">
+      <c r="E75" t="str">
         <v>TELHA GALVALUME OND 17 0,43MM 5,00M</v>
       </c>
-      <c r="E75" t="str">
+      <c r="F75" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -1678,16 +1903,19 @@
       <c r="A76">
         <v>45966.87467592592</v>
       </c>
-      <c r="B76">
+      <c r="B76" t="str">
+        <v>Conformadora de Telhas</v>
+      </c>
+      <c r="C76">
         <v>2016</v>
       </c>
-      <c r="C76">
+      <c r="D76">
         <v>212</v>
       </c>
-      <c r="D76" t="str">
+      <c r="E76" t="str">
         <v>TELHA GALVALUME OND 17 0,43MM 6,00M</v>
       </c>
-      <c r="E76" t="str">
+      <c r="F76" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -1695,16 +1923,19 @@
       <c r="A77">
         <v>45966.87467592592</v>
       </c>
-      <c r="B77">
+      <c r="B77" t="str">
+        <v>Conformadora de Telhas</v>
+      </c>
+      <c r="C77">
         <v>2015</v>
       </c>
-      <c r="C77">
+      <c r="D77">
         <v>18</v>
       </c>
-      <c r="D77" t="str">
+      <c r="E77" t="str">
         <v>TELHA GALVALUME OND 17 0,43MM 5,00M</v>
       </c>
-      <c r="E77" t="str">
+      <c r="F77" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -1712,16 +1943,19 @@
       <c r="A78">
         <v>45966.87467592592</v>
       </c>
-      <c r="B78">
+      <c r="B78" t="str">
+        <v>Conformadora de Telhas</v>
+      </c>
+      <c r="C78">
         <v>2014</v>
       </c>
-      <c r="C78">
+      <c r="D78">
         <v>18</v>
       </c>
-      <c r="D78" t="str">
+      <c r="E78" t="str">
         <v>TELHA GALVALUME OND 17 0,43MM 4,00M</v>
       </c>
-      <c r="E78" t="str">
+      <c r="F78" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -1729,16 +1963,19 @@
       <c r="A79">
         <v>45966.87467592592</v>
       </c>
-      <c r="B79">
+      <c r="B79" t="str">
+        <v>Conformadora de Telhas</v>
+      </c>
+      <c r="C79">
         <v>2013</v>
       </c>
-      <c r="C79">
+      <c r="D79">
         <v>54</v>
       </c>
-      <c r="D79" t="str">
+      <c r="E79" t="str">
         <v>TELHA GALVALUME OND 17 0,43MM 3,00M</v>
       </c>
-      <c r="E79" t="str">
+      <c r="F79" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -1746,16 +1983,19 @@
       <c r="A80">
         <v>45966.87467592592</v>
       </c>
-      <c r="B80">
-        <v>2000</v>
+      <c r="B80" t="str">
+        <v>Conformadora de Telhas</v>
       </c>
       <c r="C80">
+        <v>2000</v>
+      </c>
+      <c r="D80">
         <v>35</v>
       </c>
-      <c r="D80" t="str">
-        <v>TELHA GALVALUME TP 40 0,43MM</v>
-      </c>
       <c r="E80" t="str">
+        <v>TELHA GALVALUME TP 40 0,43MM</v>
+      </c>
+      <c r="F80" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -1763,16 +2003,19 @@
       <c r="A81">
         <v>45966.87467592592</v>
       </c>
-      <c r="B81">
+      <c r="B81" t="str">
+        <v>Conformadora de Telhas</v>
+      </c>
+      <c r="C81">
         <v>2005</v>
       </c>
-      <c r="C81">
+      <c r="D81">
         <v>5</v>
       </c>
-      <c r="D81" t="str">
+      <c r="E81" t="str">
         <v>TELHA GALVALUME TP 40 0,43MM 5,00M</v>
       </c>
-      <c r="E81" t="str">
+      <c r="F81" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -1780,16 +2023,19 @@
       <c r="A82">
         <v>45966.87467592592</v>
       </c>
-      <c r="B82">
+      <c r="B82" t="str">
+        <v>Conformadora de Telhas</v>
+      </c>
+      <c r="C82">
         <v>2004</v>
       </c>
-      <c r="C82">
+      <c r="D82">
         <v>3</v>
       </c>
-      <c r="D82" t="str">
+      <c r="E82" t="str">
         <v>TELHA GALVALUME TP 40 0,43MM 4,00M</v>
       </c>
-      <c r="E82" t="str">
+      <c r="F82" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -1797,16 +2043,19 @@
       <c r="A83">
         <v>45967.87467592592</v>
       </c>
-      <c r="B83">
+      <c r="B83" t="str">
+        <v>Conformadora de Telhas</v>
+      </c>
+      <c r="C83">
         <v>2020</v>
       </c>
-      <c r="C83">
+      <c r="D83">
         <v>200</v>
       </c>
-      <c r="D83" t="str">
+      <c r="E83" t="str">
         <v>TELHA CUMEEIRA GL TRAP 40 ABAS 300MM</v>
       </c>
-      <c r="E83" t="str">
+      <c r="F83" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -1814,16 +2063,19 @@
       <c r="A84">
         <v>45967.87467592592</v>
       </c>
-      <c r="B84">
-        <v>2000</v>
+      <c r="B84" t="str">
+        <v>Conformadora de Telhas</v>
       </c>
       <c r="C84">
+        <v>2000</v>
+      </c>
+      <c r="D84">
         <v>3</v>
       </c>
-      <c r="D84" t="str">
-        <v>TELHA GALVALUME TP 40 0,43MM</v>
-      </c>
       <c r="E84" t="str">
+        <v>TELHA GALVALUME TP 40 0,43MM</v>
+      </c>
+      <c r="F84" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -1831,16 +2083,19 @@
       <c r="A85">
         <v>45967.87467592592</v>
       </c>
-      <c r="B85">
+      <c r="B85" t="str">
+        <v>Conformadora de Telhas</v>
+      </c>
+      <c r="C85">
         <v>2005</v>
       </c>
-      <c r="C85">
+      <c r="D85">
         <v>1</v>
       </c>
-      <c r="D85" t="str">
+      <c r="E85" t="str">
         <v>TELHA GALVALUME TP 40 0,43MM 5,00M</v>
       </c>
-      <c r="E85" t="str">
+      <c r="F85" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -1848,16 +2103,19 @@
       <c r="A86">
         <v>45967.87467592592</v>
       </c>
-      <c r="B86">
+      <c r="B86" t="str">
+        <v>Conformadora de Telhas</v>
+      </c>
+      <c r="C86">
         <v>2004</v>
       </c>
-      <c r="C86">
+      <c r="D86">
         <v>3</v>
       </c>
-      <c r="D86" t="str">
+      <c r="E86" t="str">
         <v>TELHA GALVALUME TP 40 0,43MM 4,00M</v>
       </c>
-      <c r="E86" t="str">
+      <c r="F86" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -1865,16 +2123,19 @@
       <c r="A87">
         <v>45967.87467592592</v>
       </c>
-      <c r="B87">
-        <v>2000</v>
+      <c r="B87" t="str">
+        <v>Conformadora de Telhas</v>
       </c>
       <c r="C87">
+        <v>2000</v>
+      </c>
+      <c r="D87">
         <v>8</v>
       </c>
-      <c r="D87" t="str">
-        <v>TELHA GALVALUME TP 40 0,43MM</v>
-      </c>
       <c r="E87" t="str">
+        <v>TELHA GALVALUME TP 40 0,43MM</v>
+      </c>
+      <c r="F87" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -1882,16 +2143,19 @@
       <c r="A88">
         <v>45967.87467592592</v>
       </c>
-      <c r="B88">
+      <c r="B88" t="str">
+        <v>Conformadora de Telhas</v>
+      </c>
+      <c r="C88">
         <v>2003</v>
       </c>
-      <c r="C88">
+      <c r="D88">
         <v>1</v>
       </c>
-      <c r="D88" t="str">
+      <c r="E88" t="str">
         <v>TELHA GALVALUME TP 40 0,43MM 3,00M</v>
       </c>
-      <c r="E88" t="str">
+      <c r="F88" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -1899,16 +2163,19 @@
       <c r="A89">
         <v>45967.87467592592</v>
       </c>
-      <c r="B89">
+      <c r="B89" t="str">
+        <v>Conformadora de Telhas</v>
+      </c>
+      <c r="C89">
         <v>2006</v>
       </c>
-      <c r="C89">
+      <c r="D89">
         <v>300</v>
       </c>
-      <c r="D89" t="str">
+      <c r="E89" t="str">
         <v>TELHA GALVALUME TP 40 0,43MM 6,00M</v>
       </c>
-      <c r="E89" t="str">
+      <c r="F89" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -1916,16 +2183,19 @@
       <c r="A90">
         <v>45967.87467592592</v>
       </c>
-      <c r="B90">
-        <v>2000</v>
+      <c r="B90" t="str">
+        <v>Conformadora de Telhas</v>
       </c>
       <c r="C90">
+        <v>2000</v>
+      </c>
+      <c r="D90">
         <v>11</v>
       </c>
-      <c r="D90" t="str">
-        <v>TELHA GALVALUME TP 40 0,43MM</v>
-      </c>
       <c r="E90" t="str">
+        <v>TELHA GALVALUME TP 40 0,43MM</v>
+      </c>
+      <c r="F90" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -1933,16 +2203,19 @@
       <c r="A91">
         <v>45967.87467592592</v>
       </c>
-      <c r="B91">
+      <c r="B91" t="str">
+        <v>Conformadora de Telhas</v>
+      </c>
+      <c r="C91">
         <v>2003</v>
       </c>
-      <c r="C91">
+      <c r="D91">
         <v>8</v>
       </c>
-      <c r="D91" t="str">
+      <c r="E91" t="str">
         <v>TELHA GALVALUME TP 40 0,43MM 3,00M</v>
       </c>
-      <c r="E91" t="str">
+      <c r="F91" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -1950,16 +2223,19 @@
       <c r="A92">
         <v>45967.87467592592</v>
       </c>
-      <c r="B92">
-        <v>2000</v>
+      <c r="B92" t="str">
+        <v>Conformadora de Telhas</v>
       </c>
       <c r="C92">
+        <v>2000</v>
+      </c>
+      <c r="D92">
         <v>2</v>
       </c>
-      <c r="D92" t="str">
-        <v>TELHA GALVALUME TP 40 0,43MM</v>
-      </c>
       <c r="E92" t="str">
+        <v>TELHA GALVALUME TP 40 0,43MM</v>
+      </c>
+      <c r="F92" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -1967,16 +2243,19 @@
       <c r="A93">
         <v>45967.87467592592</v>
       </c>
-      <c r="B93">
+      <c r="B93" t="str">
+        <v>Conformadora de Telhas</v>
+      </c>
+      <c r="C93">
         <v>2006</v>
       </c>
-      <c r="C93">
+      <c r="D93">
         <v>16</v>
       </c>
-      <c r="D93" t="str">
+      <c r="E93" t="str">
         <v>TELHA GALVALUME TP 40 0,43MM 6,00M</v>
       </c>
-      <c r="E93" t="str">
+      <c r="F93" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -1984,16 +2263,19 @@
       <c r="A94">
         <v>45967.87467592592</v>
       </c>
-      <c r="B94">
-        <v>2000</v>
+      <c r="B94" t="str">
+        <v>Conformadora de Telhas</v>
       </c>
       <c r="C94">
+        <v>2000</v>
+      </c>
+      <c r="D94">
         <v>10</v>
       </c>
-      <c r="D94" t="str">
-        <v>TELHA GALVALUME TP 40 0,43MM</v>
-      </c>
       <c r="E94" t="str">
+        <v>TELHA GALVALUME TP 40 0,43MM</v>
+      </c>
+      <c r="F94" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -2001,16 +2283,19 @@
       <c r="A95">
         <v>45967.87467592592</v>
       </c>
-      <c r="B95">
-        <v>2000</v>
+      <c r="B95" t="str">
+        <v>Conformadora de Telhas</v>
       </c>
       <c r="C95">
+        <v>2000</v>
+      </c>
+      <c r="D95">
         <v>52</v>
       </c>
-      <c r="D95" t="str">
-        <v>TELHA GALVALUME TP 40 0,43MM</v>
-      </c>
       <c r="E95" t="str">
+        <v>TELHA GALVALUME TP 40 0,43MM</v>
+      </c>
+      <c r="F95" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -2018,16 +2303,19 @@
       <c r="A96">
         <v>45967.87467592592</v>
       </c>
-      <c r="B96">
+      <c r="B96" t="str">
+        <v>Conformadora de Telhas</v>
+      </c>
+      <c r="C96">
         <v>2005</v>
       </c>
-      <c r="C96">
+      <c r="D96">
         <v>52</v>
       </c>
-      <c r="D96" t="str">
+      <c r="E96" t="str">
         <v>TELHA GALVALUME TP 40 0,43MM 5,00M</v>
       </c>
-      <c r="E96" t="str">
+      <c r="F96" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -2035,16 +2323,19 @@
       <c r="A97">
         <v>45967.87467592592</v>
       </c>
-      <c r="B97">
-        <v>2000</v>
+      <c r="B97" t="str">
+        <v>Conformadora de Telhas</v>
       </c>
       <c r="C97">
+        <v>2000</v>
+      </c>
+      <c r="D97">
         <v>27</v>
       </c>
-      <c r="D97" t="str">
-        <v>TELHA GALVALUME TP 40 0,43MM</v>
-      </c>
       <c r="E97" t="str">
+        <v>TELHA GALVALUME TP 40 0,43MM</v>
+      </c>
+      <c r="F97" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -2052,16 +2343,19 @@
       <c r="A98">
         <v>45967.87467592592</v>
       </c>
-      <c r="B98">
-        <v>2000</v>
+      <c r="B98" t="str">
+        <v>Conformadora de Telhas</v>
       </c>
       <c r="C98">
+        <v>2000</v>
+      </c>
+      <c r="D98">
         <v>4</v>
       </c>
-      <c r="D98" t="str">
-        <v>TELHA GALVALUME TP 40 0,43MM</v>
-      </c>
       <c r="E98" t="str">
+        <v>TELHA GALVALUME TP 40 0,43MM</v>
+      </c>
+      <c r="F98" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -2069,16 +2363,19 @@
       <c r="A99">
         <v>45967.87467592592</v>
       </c>
-      <c r="B99">
-        <v>2000</v>
+      <c r="B99" t="str">
+        <v>Conformadora de Telhas</v>
       </c>
       <c r="C99">
+        <v>2000</v>
+      </c>
+      <c r="D99">
         <v>3</v>
       </c>
-      <c r="D99" t="str">
-        <v>TELHA GALVALUME TP 40 0,43MM</v>
-      </c>
       <c r="E99" t="str">
+        <v>TELHA GALVALUME TP 40 0,43MM</v>
+      </c>
+      <c r="F99" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -2086,16 +2383,19 @@
       <c r="A100">
         <v>45967.87467592592</v>
       </c>
-      <c r="B100">
-        <v>2000</v>
+      <c r="B100" t="str">
+        <v>Conformadora de Telhas</v>
       </c>
       <c r="C100">
+        <v>2000</v>
+      </c>
+      <c r="D100">
         <v>3</v>
       </c>
-      <c r="D100" t="str">
-        <v>TELHA GALVALUME TP 40 0,43MM</v>
-      </c>
       <c r="E100" t="str">
+        <v>TELHA GALVALUME TP 40 0,43MM</v>
+      </c>
+      <c r="F100" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -2103,16 +2403,19 @@
       <c r="A101">
         <v>45967.87467592592</v>
       </c>
-      <c r="B101">
-        <v>2000</v>
+      <c r="B101" t="str">
+        <v>Conformadora de Telhas</v>
       </c>
       <c r="C101">
+        <v>2000</v>
+      </c>
+      <c r="D101">
         <v>3</v>
       </c>
-      <c r="D101" t="str">
-        <v>TELHA GALVALUME TP 40 0,43MM</v>
-      </c>
       <c r="E101" t="str">
+        <v>TELHA GALVALUME TP 40 0,43MM</v>
+      </c>
+      <c r="F101" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -2120,16 +2423,19 @@
       <c r="A102">
         <v>45967.87467592592</v>
       </c>
-      <c r="B102">
+      <c r="B102" t="str">
+        <v>Conformadora de Telhas</v>
+      </c>
+      <c r="C102">
         <v>2003</v>
       </c>
-      <c r="C102">
+      <c r="D102">
         <v>6</v>
       </c>
-      <c r="D102" t="str">
+      <c r="E102" t="str">
         <v>TELHA GALVALUME TP 40 0,43MM 3,00M</v>
       </c>
-      <c r="E102" t="str">
+      <c r="F102" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -2137,16 +2443,19 @@
       <c r="A103">
         <v>45970.87467592592</v>
       </c>
-      <c r="B103">
+      <c r="B103" t="str">
+        <v>Conformadora de Telhas</v>
+      </c>
+      <c r="C103">
         <v>2015</v>
       </c>
-      <c r="C103">
+      <c r="D103">
         <v>20</v>
       </c>
-      <c r="D103" t="str">
+      <c r="E103" t="str">
         <v>TELHA GALVALUME OND 17 0,43MM 5,00M</v>
       </c>
-      <c r="E103" t="str">
+      <c r="F103" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -2154,16 +2463,19 @@
       <c r="A104">
         <v>45970.87467592592</v>
       </c>
-      <c r="B104">
+      <c r="B104" t="str">
+        <v>Conformadora de Telhas</v>
+      </c>
+      <c r="C104">
         <v>2014</v>
       </c>
-      <c r="C104">
+      <c r="D104">
         <v>21</v>
       </c>
-      <c r="D104" t="str">
+      <c r="E104" t="str">
         <v>TELHA GALVALUME OND 17 0,43MM 4,00M</v>
       </c>
-      <c r="E104" t="str">
+      <c r="F104" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -2171,16 +2483,19 @@
       <c r="A105">
         <v>45970.87467592592</v>
       </c>
-      <c r="B105">
+      <c r="B105" t="str">
+        <v>Conformadora de Telhas</v>
+      </c>
+      <c r="C105">
         <v>2017</v>
       </c>
-      <c r="C105">
+      <c r="D105">
         <v>12</v>
       </c>
-      <c r="D105" t="str">
+      <c r="E105" t="str">
         <v>TELHA GALVALUME OND 17 0,43MM 7,00M</v>
       </c>
-      <c r="E105" t="str">
+      <c r="F105" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -2188,16 +2503,19 @@
       <c r="A106">
         <v>45970.87467592592</v>
       </c>
-      <c r="B106">
+      <c r="B106" t="str">
+        <v>Conformadora de Telhas</v>
+      </c>
+      <c r="C106">
         <v>2016</v>
       </c>
-      <c r="C106">
+      <c r="D106">
         <v>14</v>
       </c>
-      <c r="D106" t="str">
+      <c r="E106" t="str">
         <v>TELHA GALVALUME OND 17 0,43MM 6,00M</v>
       </c>
-      <c r="E106" t="str">
+      <c r="F106" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -2205,16 +2523,19 @@
       <c r="A107">
         <v>45970.87467592592</v>
       </c>
-      <c r="B107">
+      <c r="B107" t="str">
+        <v>Conformadora de Telhas</v>
+      </c>
+      <c r="C107">
         <v>2015</v>
       </c>
-      <c r="C107">
+      <c r="D107">
         <v>8</v>
       </c>
-      <c r="D107" t="str">
+      <c r="E107" t="str">
         <v>TELHA GALVALUME OND 17 0,43MM 5,00M</v>
       </c>
-      <c r="E107" t="str">
+      <c r="F107" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -2222,16 +2543,19 @@
       <c r="A108">
         <v>45970.87467592592</v>
       </c>
-      <c r="B108">
+      <c r="B108" t="str">
+        <v>Conformadora de Telhas</v>
+      </c>
+      <c r="C108">
         <v>2014</v>
       </c>
-      <c r="C108">
+      <c r="D108">
         <v>29</v>
       </c>
-      <c r="D108" t="str">
+      <c r="E108" t="str">
         <v>TELHA GALVALUME OND 17 0,43MM 4,00M</v>
       </c>
-      <c r="E108" t="str">
+      <c r="F108" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -2239,16 +2563,19 @@
       <c r="A109">
         <v>45970.87467592592</v>
       </c>
-      <c r="B109">
+      <c r="B109" t="str">
+        <v>Conformadora de Telhas</v>
+      </c>
+      <c r="C109">
         <v>2014</v>
       </c>
-      <c r="C109">
+      <c r="D109">
         <v>14</v>
       </c>
-      <c r="D109" t="str">
+      <c r="E109" t="str">
         <v>TELHA GALVALUME OND 17 0,43MM 4,00M</v>
       </c>
-      <c r="E109" t="str">
+      <c r="F109" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -2257,15 +2584,18 @@
         <v>45971.87467592592</v>
       </c>
       <c r="B110" t="str">
+        <v>Perfil "U" ZL</v>
+      </c>
+      <c r="C110" t="str">
         <v>00664D</v>
       </c>
-      <c r="C110">
+      <c r="D110">
         <v>88</v>
       </c>
-      <c r="D110" t="str">
+      <c r="E110" t="str">
         <v>PERFIL US 150X50X2,65</v>
       </c>
-      <c r="E110" t="str">
+      <c r="F110" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -2274,15 +2604,18 @@
         <v>45971.87467592592</v>
       </c>
       <c r="B111" t="str">
+        <v>Perfil "U" ZL</v>
+      </c>
+      <c r="C111" t="str">
         <v>00664E</v>
       </c>
-      <c r="C111">
+      <c r="D111">
         <v>158</v>
       </c>
-      <c r="D111" t="str">
+      <c r="E111" t="str">
         <v>PERFIL US 150X50X3,00</v>
       </c>
-      <c r="E111" t="str">
+      <c r="F111" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -2290,16 +2623,19 @@
       <c r="A112">
         <v>45972.87467592592</v>
       </c>
-      <c r="B112">
-        <v>2000</v>
+      <c r="B112" t="str">
+        <v>Conformadora de Telhas</v>
       </c>
       <c r="C112">
+        <v>2000</v>
+      </c>
+      <c r="D112">
         <v>48</v>
       </c>
-      <c r="D112" t="str">
-        <v>TELHA GALVALUME TP 40 0,43MM</v>
-      </c>
       <c r="E112" t="str">
+        <v>TELHA GALVALUME TP 40 0,43MM</v>
+      </c>
+      <c r="F112" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -2307,16 +2643,19 @@
       <c r="A113">
         <v>45972.87467592592</v>
       </c>
-      <c r="B113">
+      <c r="B113" t="str">
+        <v>Conformadora de Telhas</v>
+      </c>
+      <c r="C113">
         <v>2020</v>
       </c>
-      <c r="C113">
+      <c r="D113">
         <v>100</v>
       </c>
-      <c r="D113" t="str">
+      <c r="E113" t="str">
         <v>TELHA CUMEEIRA GL TRAP 40 ABAS 300MM</v>
       </c>
-      <c r="E113" t="str">
+      <c r="F113" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -2324,16 +2663,19 @@
       <c r="A114">
         <v>45972.87467592592</v>
       </c>
-      <c r="B114">
+      <c r="B114" t="str">
+        <v>Conformadora de Telhas</v>
+      </c>
+      <c r="C114">
         <v>2006</v>
       </c>
-      <c r="C114">
+      <c r="D114">
         <v>300</v>
       </c>
-      <c r="D114" t="str">
+      <c r="E114" t="str">
         <v>TELHA GALVALUME TP 40 0,43MM 6,00M</v>
       </c>
-      <c r="E114" t="str">
+      <c r="F114" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -2341,16 +2683,19 @@
       <c r="A115">
         <v>45972.87467592592</v>
       </c>
-      <c r="B115">
+      <c r="B115" t="str">
+        <v>Conformadora de Telhas</v>
+      </c>
+      <c r="C115">
         <v>2017</v>
       </c>
-      <c r="C115">
+      <c r="D115">
         <v>21</v>
       </c>
-      <c r="D115" t="str">
+      <c r="E115" t="str">
         <v>TELHA GALVALUME OND 17 0,43MM 7,00M</v>
       </c>
-      <c r="E115" t="str">
+      <c r="F115" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -2358,16 +2703,19 @@
       <c r="A116">
         <v>45972.87467592592</v>
       </c>
-      <c r="B116">
-        <v>2000</v>
+      <c r="B116" t="str">
+        <v>Conformadora de Telhas</v>
       </c>
       <c r="C116">
+        <v>2000</v>
+      </c>
+      <c r="D116">
         <v>21</v>
       </c>
-      <c r="D116" t="str">
-        <v>TELHA GALVALUME TP 40 0,43MM</v>
-      </c>
       <c r="E116" t="str">
+        <v>TELHA GALVALUME TP 40 0,43MM</v>
+      </c>
+      <c r="F116" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -2375,16 +2723,19 @@
       <c r="A117">
         <v>45972.87467592592</v>
       </c>
-      <c r="B117">
+      <c r="B117" t="str">
+        <v>Conformadora de Telhas</v>
+      </c>
+      <c r="C117">
         <v>2014</v>
       </c>
-      <c r="C117">
+      <c r="D117">
         <v>10</v>
       </c>
-      <c r="D117" t="str">
+      <c r="E117" t="str">
         <v>TELHA GALVALUME OND 17 0,43MM 4,00M</v>
       </c>
-      <c r="E117" t="str">
+      <c r="F117" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -2392,16 +2743,19 @@
       <c r="A118">
         <v>45972.87467592592</v>
       </c>
-      <c r="B118">
-        <v>2000</v>
+      <c r="B118" t="str">
+        <v>Conformadora de Telhas</v>
       </c>
       <c r="C118">
+        <v>2000</v>
+      </c>
+      <c r="D118">
         <v>10</v>
       </c>
-      <c r="D118" t="str">
-        <v>TELHA GALVALUME TP 40 0,43MM</v>
-      </c>
       <c r="E118" t="str">
+        <v>TELHA GALVALUME TP 40 0,43MM</v>
+      </c>
+      <c r="F118" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -2409,16 +2763,19 @@
       <c r="A119">
         <v>45972.87467592592</v>
       </c>
-      <c r="B119">
-        <v>2000</v>
+      <c r="B119" t="str">
+        <v>Conformadora de Telhas</v>
       </c>
       <c r="C119">
+        <v>2000</v>
+      </c>
+      <c r="D119">
         <v>10</v>
       </c>
-      <c r="D119" t="str">
-        <v>TELHA GALVALUME TP 40 0,43MM</v>
-      </c>
       <c r="E119" t="str">
+        <v>TELHA GALVALUME TP 40 0,43MM</v>
+      </c>
+      <c r="F119" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -2426,16 +2783,19 @@
       <c r="A120">
         <v>45972.87467592592</v>
       </c>
-      <c r="B120">
+      <c r="B120" t="str">
+        <v>Conformadora de Telhas</v>
+      </c>
+      <c r="C120">
         <v>2017</v>
       </c>
-      <c r="C120">
+      <c r="D120">
         <v>100</v>
       </c>
-      <c r="D120" t="str">
+      <c r="E120" t="str">
         <v>TELHA GALVALUME OND 17 0,43MM 7,00M</v>
       </c>
-      <c r="E120" t="str">
+      <c r="F120" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -2443,16 +2803,19 @@
       <c r="A121">
         <v>45972.87467592592</v>
       </c>
-      <c r="B121">
+      <c r="B121" t="str">
+        <v>Conformadora de Telhas</v>
+      </c>
+      <c r="C121">
         <v>2016</v>
       </c>
-      <c r="C121">
+      <c r="D121">
         <v>100</v>
       </c>
-      <c r="D121" t="str">
+      <c r="E121" t="str">
         <v>TELHA GALVALUME OND 17 0,43MM 6,00M</v>
       </c>
-      <c r="E121" t="str">
+      <c r="F121" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -2460,16 +2823,19 @@
       <c r="A122">
         <v>45974.87467592592</v>
       </c>
-      <c r="B122">
+      <c r="B122" t="str">
+        <v>Conformadora de Telhas</v>
+      </c>
+      <c r="C122">
         <v>2006</v>
       </c>
-      <c r="C122">
+      <c r="D122">
         <v>10</v>
       </c>
-      <c r="D122" t="str">
+      <c r="E122" t="str">
         <v>TELHA GALVALUME TP 40 0,43MM 6,00M</v>
       </c>
-      <c r="E122" t="str">
+      <c r="F122" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -2477,16 +2843,19 @@
       <c r="A123">
         <v>45974.87467592592</v>
       </c>
-      <c r="B123">
+      <c r="B123" t="str">
+        <v>Conformadora de Telhas</v>
+      </c>
+      <c r="C123">
         <v>2004</v>
       </c>
-      <c r="C123">
+      <c r="D123">
         <v>2</v>
       </c>
-      <c r="D123" t="str">
+      <c r="E123" t="str">
         <v>TELHA GALVALUME TP 40 0,43MM 4,00M</v>
       </c>
-      <c r="E123" t="str">
+      <c r="F123" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -2494,16 +2863,19 @@
       <c r="A124">
         <v>45974.87467592592</v>
       </c>
-      <c r="B124">
+      <c r="B124" t="str">
+        <v>Conformadora de Telhas</v>
+      </c>
+      <c r="C124">
         <v>2006</v>
       </c>
-      <c r="C124">
+      <c r="D124">
         <v>150</v>
       </c>
-      <c r="D124" t="str">
+      <c r="E124" t="str">
         <v>TELHA GALVALUME TP 40 0,43MM 6,00M</v>
       </c>
-      <c r="E124" t="str">
+      <c r="F124" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -2511,16 +2883,19 @@
       <c r="A125">
         <v>45974.87467592592</v>
       </c>
-      <c r="B125">
+      <c r="B125" t="str">
+        <v>Conformadora de Telhas</v>
+      </c>
+      <c r="C125">
         <v>2007</v>
       </c>
-      <c r="C125">
+      <c r="D125">
         <v>10</v>
       </c>
-      <c r="D125" t="str">
+      <c r="E125" t="str">
         <v>TELHA GALVALUME TP 40 0,43MM 7,00M</v>
       </c>
-      <c r="E125" t="str">
+      <c r="F125" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -2528,16 +2903,19 @@
       <c r="A126">
         <v>45974.87467592592</v>
       </c>
-      <c r="B126">
+      <c r="B126" t="str">
+        <v>Conformadora de Telhas</v>
+      </c>
+      <c r="C126">
         <v>2006</v>
       </c>
-      <c r="C126">
+      <c r="D126">
         <v>4</v>
       </c>
-      <c r="D126" t="str">
+      <c r="E126" t="str">
         <v>TELHA GALVALUME TP 40 0,43MM 6,00M</v>
       </c>
-      <c r="E126" t="str">
+      <c r="F126" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -2545,16 +2923,19 @@
       <c r="A127">
         <v>45974.87467592592</v>
       </c>
-      <c r="B127">
+      <c r="B127" t="str">
+        <v>Conformadora de Telhas</v>
+      </c>
+      <c r="C127">
         <v>2005</v>
       </c>
-      <c r="C127">
+      <c r="D127">
         <v>8</v>
       </c>
-      <c r="D127" t="str">
+      <c r="E127" t="str">
         <v>TELHA GALVALUME TP 40 0,43MM 5,00M</v>
       </c>
-      <c r="E127" t="str">
+      <c r="F127" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -2562,16 +2943,19 @@
       <c r="A128">
         <v>45974.87467592592</v>
       </c>
-      <c r="B128">
+      <c r="B128" t="str">
+        <v>Conformadora de Telhas</v>
+      </c>
+      <c r="C128">
         <v>2004</v>
       </c>
-      <c r="C128">
+      <c r="D128">
         <v>15</v>
       </c>
-      <c r="D128" t="str">
+      <c r="E128" t="str">
         <v>TELHA GALVALUME TP 40 0,43MM 4,00M</v>
       </c>
-      <c r="E128" t="str">
+      <c r="F128" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -2579,16 +2963,19 @@
       <c r="A129">
         <v>45974.87467592592</v>
       </c>
-      <c r="B129">
+      <c r="B129" t="str">
+        <v>Conformadora de Telhas</v>
+      </c>
+      <c r="C129">
         <v>2006</v>
       </c>
-      <c r="C129">
+      <c r="D129">
         <v>11</v>
       </c>
-      <c r="D129" t="str">
+      <c r="E129" t="str">
         <v>TELHA GALVALUME TP 40 0,43MM 6,00M</v>
       </c>
-      <c r="E129" t="str">
+      <c r="F129" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -2596,16 +2983,19 @@
       <c r="A130">
         <v>45974.87467592592</v>
       </c>
-      <c r="B130">
+      <c r="B130" t="str">
+        <v>Conformadora de Telhas</v>
+      </c>
+      <c r="C130">
         <v>2005</v>
       </c>
-      <c r="C130">
+      <c r="D130">
         <v>100</v>
       </c>
-      <c r="D130" t="str">
+      <c r="E130" t="str">
         <v>TELHA GALVALUME TP 40 0,43MM 5,00M</v>
       </c>
-      <c r="E130" t="str">
+      <c r="F130" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -2613,16 +3003,19 @@
       <c r="A131">
         <v>45974.87467592592</v>
       </c>
-      <c r="B131">
-        <v>2000</v>
+      <c r="B131" t="str">
+        <v>Conformadora de Telhas</v>
       </c>
       <c r="C131">
+        <v>2000</v>
+      </c>
+      <c r="D131">
         <v>36</v>
       </c>
-      <c r="D131" t="str">
-        <v>TELHA GALVALUME TP 40 0,43MM</v>
-      </c>
       <c r="E131" t="str">
+        <v>TELHA GALVALUME TP 40 0,43MM</v>
+      </c>
+      <c r="F131" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -2630,16 +3023,19 @@
       <c r="A132">
         <v>45974.87467592592</v>
       </c>
-      <c r="B132">
-        <v>2000</v>
+      <c r="B132" t="str">
+        <v>Conformadora de Telhas</v>
       </c>
       <c r="C132">
+        <v>2000</v>
+      </c>
+      <c r="D132">
         <v>34</v>
       </c>
-      <c r="D132" t="str">
-        <v>TELHA GALVALUME TP 40 0,43MM</v>
-      </c>
       <c r="E132" t="str">
+        <v>TELHA GALVALUME TP 40 0,43MM</v>
+      </c>
+      <c r="F132" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -2647,16 +3043,19 @@
       <c r="A133">
         <v>45974.87467592592</v>
       </c>
-      <c r="B133">
+      <c r="B133" t="str">
+        <v>Conformadora de Telhas</v>
+      </c>
+      <c r="C133">
         <v>2016</v>
       </c>
-      <c r="C133">
+      <c r="D133">
         <v>10</v>
       </c>
-      <c r="D133" t="str">
+      <c r="E133" t="str">
         <v>TELHA GALVALUME OND 17 0,43MM 6,00M</v>
       </c>
-      <c r="E133" t="str">
+      <c r="F133" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -2664,16 +3063,19 @@
       <c r="A134">
         <v>45974.87467592592</v>
       </c>
-      <c r="B134">
+      <c r="B134" t="str">
+        <v>Conformadora de Telhas</v>
+      </c>
+      <c r="C134">
         <v>2015</v>
       </c>
-      <c r="C134">
+      <c r="D134">
         <v>5</v>
       </c>
-      <c r="D134" t="str">
+      <c r="E134" t="str">
         <v>TELHA GALVALUME OND 17 0,43MM 5,00M</v>
       </c>
-      <c r="E134" t="str">
+      <c r="F134" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -2681,16 +3083,19 @@
       <c r="A135">
         <v>45974.87467592592</v>
       </c>
-      <c r="B135">
+      <c r="B135" t="str">
+        <v>Conformadora de Telhas</v>
+      </c>
+      <c r="C135">
         <v>2014</v>
       </c>
-      <c r="C135">
+      <c r="D135">
         <v>10</v>
       </c>
-      <c r="D135" t="str">
+      <c r="E135" t="str">
         <v>TELHA GALVALUME OND 17 0,43MM 4,00M</v>
       </c>
-      <c r="E135" t="str">
+      <c r="F135" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -2698,16 +3103,19 @@
       <c r="A136">
         <v>45974.87467592592</v>
       </c>
-      <c r="B136">
+      <c r="B136" t="str">
+        <v>Conformadora de Telhas</v>
+      </c>
+      <c r="C136">
         <v>2013</v>
       </c>
-      <c r="C136">
+      <c r="D136">
         <v>5</v>
       </c>
-      <c r="D136" t="str">
+      <c r="E136" t="str">
         <v>TELHA GALVALUME OND 17 0,43MM 3,00M</v>
       </c>
-      <c r="E136" t="str">
+      <c r="F136" t="str">
         <v>Estoque</v>
       </c>
     </row>
@@ -2716,21 +3124,24 @@
         <v>45974.87467592592</v>
       </c>
       <c r="B137" t="str">
+        <v>Perfil "U" BR200 Regiane</v>
+      </c>
+      <c r="C137" t="str">
         <v>00651a</v>
       </c>
-      <c r="C137">
+      <c r="D137">
         <v>241</v>
       </c>
-      <c r="D137" t="str">
+      <c r="E137" t="str">
         <v>PERFIL US 50X25X1,80</v>
       </c>
-      <c r="E137" t="str">
+      <c r="F137" t="str">
         <v>Estoque</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E137"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F137"/>
   </ignoredErrors>
 </worksheet>
 </file>